--- a/backtest_runs/20260410_193731/by_symbol/KOHE/KOHE.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/KOHE/KOHE.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
         <v>-4202.68</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>98043.58</v>
@@ -679,7 +679,7 @@
         <v>-3333.160000000006</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>94710.42</v>
@@ -817,7 +817,7 @@
         <v>-1666.580000000003</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>99637.7</v>
@@ -955,7 +955,7 @@
         <v>-1014.440000000004</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>99565.23999999999</v>
@@ -1047,7 +1047,7 @@
         <v>-1014.439999999991</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>99855.08</v>
@@ -1093,7 +1093,7 @@
         <v>-217.3800000000082</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>99637.7</v>
@@ -1185,7 +1185,7 @@
         <v>-289.8399999999938</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>101666.58</v>
@@ -1231,7 +1231,7 @@
         <v>-797.0600000000087</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>100869.52</v>
@@ -1277,7 +1277,7 @@
         <v>-2608.559999999996</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>98260.95999999999</v>
@@ -1323,7 +1323,7 @@
         <v>-1231.819999999999</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>97029.14</v>
@@ -1415,7 +1415,7 @@
         <v>-1159.360000000001</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>97608.81999999999</v>
@@ -1507,7 +1507,7 @@
         <v>-217.3799999999954</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>98768.17999999999</v>
@@ -1553,7 +1553,7 @@
         <v>-1231.819999999999</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>97536.36</v>
@@ -1645,7 +1645,7 @@
         <v>-3550.540000000001</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>98188.5</v>
